--- a/Unity/Assets/Config/Excel/MonsterPositionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/MonsterPositionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterGroupProto" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -148,34 +148,25 @@
     <t>int</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>-15,0.00,2.2</t>
-  </si>
-  <si>
-    <t>13.84,0.00,-20.09</t>
-  </si>
-  <si>
-    <t>6.19,0.00,-1.74</t>
-  </si>
-  <si>
-    <t>-7.86,0.00,-29.54</t>
-  </si>
-  <si>
-    <t>0.66,0.00,-31.84</t>
-  </si>
-  <si>
-    <t>-19.47,0.00,-24.91</t>
-  </si>
-  <si>
-    <t>-19.45,0.00,-9.23</t>
+    <t>1217,0,-451</t>
+  </si>
+  <si>
+    <t>1217,0,309</t>
+  </si>
+  <si>
+    <t>-931,0,309</t>
+  </si>
+  <si>
+    <t>-931,0,-503</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1572,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{F2AFD912-FB6D-489E-8D3E-5A9528A50209}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{07364AD4-FC01-47A6-9F0F-D060EB4E67CC}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1968,19 +1959,19 @@
         <v>19</v>
       </c>
       <c r="G5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="I5" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
@@ -2020,7 +2011,7 @@
       <c r="E7" s="6">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G7" s="6">
@@ -2047,7 +2038,7 @@
       <c r="E8" s="6">
         <v>2</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G8" s="6">
@@ -2069,12 +2060,12 @@
         <v>10004</v>
       </c>
       <c r="D9" s="6">
-        <v>10005</v>
+        <v>0</v>
       </c>
       <c r="E9" s="6">
         <v>2</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="6">
@@ -2092,84 +2083,36 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
-      <c r="C10" s="6">
-        <v>10005</v>
-      </c>
-      <c r="D10" s="6">
-        <v>10006</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6">
-        <v>310101</v>
-      </c>
-      <c r="H10" s="6">
-        <v>5</v>
-      </c>
-      <c r="I10" s="6">
-        <v>2</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
-      <c r="C11" s="6">
-        <v>10006</v>
-      </c>
-      <c r="D11" s="6">
-        <v>10007</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="6">
-        <v>310101</v>
-      </c>
-      <c r="H11" s="6">
-        <v>5</v>
-      </c>
-      <c r="I11" s="6">
-        <v>2</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
-      <c r="C12" s="6">
-        <v>10007</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="6">
-        <v>310101</v>
-      </c>
-      <c r="H12" s="6">
-        <v>4</v>
-      </c>
-      <c r="I12" s="6">
-        <v>2</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="6"/>
     </row>
   </sheetData>
